--- a/data/trans_camb/P3A_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 1,15</t>
+          <t>-5,16; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,79</t>
+          <t>-5,49; 0,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,2</t>
+          <t>-3,68; 3,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,26</t>
+          <t>-1,53; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,85</t>
+          <t>-2,29; 4,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,76</t>
+          <t>-0,14; 5,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,03</t>
+          <t>-2,33; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,56</t>
+          <t>-2,9; 1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,76</t>
+          <t>-0,91; 3,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,7; 53,44</t>
+          <t>-79,23; 47,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,42; 38,24</t>
+          <t>-80,2; 37,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 109,52</t>
+          <t>-55,47; 107,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 439,83</t>
+          <t>-44,47; 491,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,79; 302,98</t>
+          <t>-62,96; 449,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 444,26</t>
+          <t>-7,04; 507,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 86,68</t>
+          <t>-50,23; 86,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 59,88</t>
+          <t>-65,61; 68,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 155,87</t>
+          <t>-18,54; 157,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,85</t>
+          <t>-4,03; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -0,37</t>
+          <t>-4,78; -0,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,28</t>
+          <t>-2,95; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,83</t>
+          <t>-1,16; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,31</t>
+          <t>-3,52; 0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,35</t>
+          <t>-1,0; 3,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,65</t>
+          <t>-1,74; 1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,19</t>
+          <t>-3,24; -0,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,06</t>
+          <t>-1,21; 2,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 40,59</t>
+          <t>-76,39; 53,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,7; -10,08</t>
+          <t>-87,45; -18,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 96,34</t>
+          <t>-58,59; 90,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 172,14</t>
+          <t>-29,78; 190,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 65,91</t>
+          <t>-74,5; 45,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 151,33</t>
+          <t>-26,09; 154,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 61,87</t>
+          <t>-39,77; 67,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,12; -4,46</t>
+          <t>-71,54; 1,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 78,69</t>
+          <t>-29,06; 78,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,13</t>
+          <t>-1,73; 5,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,71</t>
+          <t>-4,44; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 5,88</t>
+          <t>-1,12; 5,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,54</t>
+          <t>-2,22; 4,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,02</t>
+          <t>-5,38; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,47</t>
+          <t>1,91; 8,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,95</t>
+          <t>-1,15; 3,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,33</t>
+          <t>-4,22; -0,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,07</t>
+          <t>1,53; 6,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 183,22</t>
+          <t>-32,6; 194,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,94; 28,39</t>
+          <t>-73,6; 48,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 220,38</t>
+          <t>-22,19; 204,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 157,72</t>
+          <t>-42,57; 193,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,37; 13,25</t>
+          <t>-87,8; 22,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,26; 314,19</t>
+          <t>29,94; 346,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 131,9</t>
+          <t>-21,67; 122,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,41; -6,0</t>
+          <t>-74,02; -1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,47; 198,29</t>
+          <t>25,29; 209,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,39</t>
+          <t>-3,11; 2,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,38</t>
+          <t>-5,03; -0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,54</t>
+          <t>1,15; 9,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,02</t>
+          <t>-4,71; 1,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,76</t>
+          <t>-5,24; 1,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,77</t>
+          <t>-3,2; 2,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,78</t>
+          <t>-3,01; 0,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -0,41</t>
+          <t>-4,22; -0,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,38</t>
+          <t>-0,63; 4,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 105,37</t>
+          <t>-64,6; 112,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,26; -4,03</t>
+          <t>-91,18; 7,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 390,26</t>
+          <t>18,92; 404,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 33,48</t>
+          <t>-65,61; 39,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,96; 30,21</t>
+          <t>-76,7; 39,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 70,48</t>
+          <t>-44,97; 79,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 23,04</t>
+          <t>-55,32; 26,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,57; -8,06</t>
+          <t>-75,62; -4,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 126,65</t>
+          <t>-11,5; 125,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,11</t>
+          <t>-1,76; 6,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,06</t>
+          <t>-5,62; 0,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,72</t>
+          <t>-3,72; 2,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,2</t>
+          <t>0,95; 7,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,59</t>
+          <t>-1,7; 2,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,32</t>
+          <t>-0,01; 4,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,52</t>
+          <t>0,4; 5,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,79</t>
+          <t>-2,99; 0,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,93</t>
+          <t>-1,12; 2,9</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 334,91</t>
+          <t>-45,36; 417,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,54</t>
+          <t>-100,0; 115,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 210,43</t>
+          <t>-70,14; 167,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,77; —</t>
+          <t>-11,34; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,29; —</t>
+          <t>-16,97; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 478,77</t>
+          <t>1,12; 487,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 90,88</t>
+          <t>-89,75; 64,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 248,03</t>
+          <t>-34,29; 251,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 9,4</t>
+          <t>0,59; 9,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,29</t>
+          <t>-5,23; 0,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,87</t>
+          <t>-1,8; 4,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,4</t>
+          <t>0,05; 5,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,64</t>
+          <t>1,05; 7,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,21</t>
+          <t>4,89; 10,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,4</t>
+          <t>1,21; 6,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,16</t>
+          <t>-1,25; 3,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,09</t>
+          <t>2,23; 6,89</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 326,7</t>
+          <t>-1,25; 314,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 64,54</t>
+          <t>-78,43; 39,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 172,05</t>
+          <t>-28,97; 190,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 1204,79</t>
+          <t>-32,47; 1013,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1379,79</t>
+          <t>15,95; 1371,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>138,07; 2320,1</t>
+          <t>144,22; 2303,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,16; 298,83</t>
+          <t>26,82; 310,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 148,05</t>
+          <t>-33,03; 167,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43,47; 357,51</t>
+          <t>50,42; 359,9</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,85</t>
+          <t>-2,19; 1,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,69</t>
+          <t>-1,5; 2,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,28</t>
+          <t>0,02; 5,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,68</t>
+          <t>0,07; 4,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,03</t>
+          <t>-1,07; 3,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,53</t>
+          <t>-1,65; 4,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,71</t>
+          <t>-0,47; 2,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,34</t>
+          <t>-0,64; 2,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,92</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 86,77</t>
+          <t>-52,3; 81,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 126,27</t>
+          <t>-37,67; 137,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 228,15</t>
+          <t>-5,86; 225,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,37; 256,97</t>
+          <t>-4,0; 233,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 154,51</t>
+          <t>-31,57; 144,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 203,39</t>
+          <t>-34,48; 216,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 113,8</t>
+          <t>-14,46; 117,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 101,29</t>
+          <t>-18,15; 97,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 164,61</t>
+          <t>3,24; 176,68</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,21</t>
+          <t>-3,68; 0,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,1</t>
+          <t>-3,92; -0,11</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -1,69</t>
+          <t>-5,6; -1,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,01</t>
+          <t>-0,69; 3,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,47</t>
+          <t>-2,09; 1,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,78</t>
+          <t>-1,41; 1,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,25</t>
+          <t>-1,59; 1,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,35</t>
+          <t>-2,38; 0,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,5</t>
+          <t>-3,19; -0,48</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 5,61</t>
+          <t>-61,89; 7,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,89; 1,68</t>
+          <t>-64,58; -0,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-90,45; -46,7</t>
+          <t>-89,25; -46,67</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 125,17</t>
+          <t>-16,68; 134,86</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 70,27</t>
+          <t>-51,99; 62,19</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 84,37</t>
+          <t>-32,0; 88,67</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 37,76</t>
+          <t>-33,63; 35,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 11,7</t>
+          <t>-50,9; 6,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-66,19; -17,79</t>
+          <t>-66,09; -13,06</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,72</t>
+          <t>-1,24; 0,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,68</t>
+          <t>-2,55; -0,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,44</t>
+          <t>-0,82; 1,33</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,39</t>
+          <t>0,42; 2,3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,73</t>
+          <t>-0,97; 0,76</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,13</t>
+          <t>1,1; 3,18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,33</t>
+          <t>-0,07; 1,24</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,2</t>
+          <t>-1,49; -0,21</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,98</t>
+          <t>0,38; 1,95</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 20,27</t>
+          <t>-26,95; 22,32</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -19,28</t>
+          <t>-55,87; -21,45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 39,43</t>
+          <t>-18,74; 36,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,32; 86,73</t>
+          <t>11,17; 84,88</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 27,08</t>
+          <t>-28,0; 27,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,33; 115,71</t>
+          <t>32,24; 116,92</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 41,31</t>
+          <t>-2,03; 37,37</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -6,05</t>
+          <t>-38,48; -7,08</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,23; 60,35</t>
+          <t>10,12; 58,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,88</t>
+          <t>-5,5; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,67</t>
+          <t>-5,62; 0,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,14</t>
+          <t>-3,34; 2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,9</t>
+          <t>-1,06; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,01</t>
+          <t>-2,33; 4,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,7</t>
+          <t>-0,03; 5,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,03</t>
+          <t>-2,68; 1,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,46</t>
+          <t>-3,1; 1,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,65</t>
+          <t>-1,05; 3,21</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>-7,05%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122,12%</t>
+          <t>110,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,23; 47,83</t>
+          <t>-81,05; 35,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,2; 37,26</t>
+          <t>-83,85; 40,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 107,86</t>
+          <t>-50,07; 116,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 491,33</t>
+          <t>-39,05; 446,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 449,89</t>
+          <t>-67,26; 323,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 507,06</t>
+          <t>-8,26; 554,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 86,98</t>
+          <t>-53,26; 75,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 68,34</t>
+          <t>-63,14; 56,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 157,12</t>
+          <t>-22,94; 132,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,82</t>
+          <t>-3,86; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,7</t>
+          <t>-4,76; -0,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,16</t>
+          <t>-2,87; 2,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,04</t>
+          <t>-1,27; 3,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,9</t>
+          <t>-3,2; 1,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,31</t>
+          <t>-0,78; 3,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,72</t>
+          <t>-1,76; 1,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,15</t>
+          <t>-3,26; -0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,13</t>
+          <t>-1,02; 2,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,75%</t>
+          <t>-9,32%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,39; 53,07</t>
+          <t>-74,97; 45,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,45; -18,17</t>
+          <t>-86,37; -7,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 90,71</t>
+          <t>-56,85; 89,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 190,42</t>
+          <t>-31,06; 178,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,5; 45,39</t>
+          <t>-72,61; 60,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 154,03</t>
+          <t>-18,64; 164,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 67,29</t>
+          <t>-40,72; 58,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 1,87</t>
+          <t>-72,84; -5,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 78,17</t>
+          <t>-24,24; 89,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>4,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>3,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,28</t>
+          <t>-1,76; 5,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,87</t>
+          <t>-4,55; 0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,5</t>
+          <t>-0,82; 5,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,77</t>
+          <t>-2,0; 4,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,12</t>
+          <t>-5,3; 0,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 8,35</t>
+          <t>1,56; 8,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,82</t>
+          <t>-0,9; 3,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,22</t>
+          <t>-4,03; -0,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,23</t>
+          <t>1,47; 5,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>124,62%</t>
+          <t>121,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 194,98</t>
+          <t>-33,6; 173,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 48,68</t>
+          <t>-77,01; 45,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 204,11</t>
+          <t>-15,57; 200,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 193,6</t>
+          <t>-41,16; 162,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 22,29</t>
+          <t>-89,47; 13,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,94; 346,77</t>
+          <t>18,37; 303,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 122,37</t>
+          <t>-18,57; 118,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,02; -1,6</t>
+          <t>-74,2; 2,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,29; 209,51</t>
+          <t>24,61; 188,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,33</t>
+          <t>-3,28; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,41</t>
+          <t>-4,76; -0,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,14</t>
+          <t>0,67; 8,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,07</t>
+          <t>-4,57; 0,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 1,0</t>
+          <t>-5,28; 1,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,97</t>
+          <t>-1,83; 3,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,85</t>
+          <t>-3,17; 0,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,32</t>
+          <t>-4,41; -0,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,41</t>
+          <t>0,69; 5,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125,8%</t>
+          <t>123,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 112,61</t>
+          <t>-65,72; 72,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,18; 7,7</t>
+          <t>-89,98; -1,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,92; 404,88</t>
+          <t>8,39; 393,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,61; 39,21</t>
+          <t>-68,19; 27,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 39,61</t>
+          <t>-79,37; 34,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 79,36</t>
+          <t>-26,82; 99,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 26,73</t>
+          <t>-55,29; 28,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,62; -4,22</t>
+          <t>-78,9; -4,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 125,61</t>
+          <t>9,0; 160,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,41</t>
+          <t>-2,23; 6,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,07</t>
+          <t>-5,43; 0,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,73</t>
+          <t>-3,83; 2,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,05</t>
+          <t>0,74; 7,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,83</t>
+          <t>-1,6; 2,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,55</t>
+          <t>0,6; 5,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,48</t>
+          <t>0,37; 5,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,59</t>
+          <t>-2,74; 0,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,9</t>
+          <t>-0,71; 3,01</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,86%</t>
+          <t>-12,93%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>230,08%</t>
+          <t>290,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 417,87</t>
+          <t>-56,63; 309,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,37</t>
+          <t>-100,0; 79,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,14; 167,95</t>
+          <t>-73,11; 173,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,34; —</t>
+          <t>-9,9; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,97; —</t>
+          <t>3,99; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,12; 487,28</t>
+          <t>0,79; 451,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 64,79</t>
+          <t>-86,49; 79,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,29; 251,37</t>
+          <t>-25,82; 245,03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 9,01</t>
+          <t>0,46; 9,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,96</t>
+          <t>-5,08; 1,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,92</t>
+          <t>-2,0; 4,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,71</t>
+          <t>0,01; 5,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,78</t>
+          <t>0,73; 7,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,67</t>
+          <t>4,56; 10,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,46</t>
+          <t>1,32; 6,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,32</t>
+          <t>-1,45; 3,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,89</t>
+          <t>2,39; 6,81</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>508,4%</t>
+          <t>496,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>154,91%</t>
+          <t>151,21%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 314,29</t>
+          <t>1,91; 331,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-78,43; 39,3</t>
+          <t>-79,82; 53,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 190,86</t>
+          <t>-32,21; 166,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 1013,79</t>
+          <t>-17,64; 1066,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,95; 1371,92</t>
+          <t>6,8; 1671,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>144,22; 2303,52</t>
+          <t>118,68; 2158,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,82; 310,86</t>
+          <t>26,35; 339,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 167,85</t>
+          <t>-35,79; 167,24</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,42; 359,9</t>
+          <t>49,97; 342,01</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>3,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,86</t>
+          <t>-2,48; 1,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,94</t>
+          <t>-1,72; 2,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,18</t>
+          <t>0,35; 5,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,58</t>
+          <t>-0,02; 4,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,05</t>
+          <t>-0,97; 3,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,6</t>
+          <t>1,99; 6,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,75</t>
+          <t>-0,41; 2,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,33</t>
+          <t>-0,62; 2,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>1,86; 5,04</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>143,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>112,58%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 81,95</t>
+          <t>-54,06; 92,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 137,86</t>
+          <t>-41,0; 125,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 225,45</t>
+          <t>4,13; 238,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 233,45</t>
+          <t>-4,82; 239,51</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 144,7</t>
+          <t>-29,74; 160,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 216,18</t>
+          <t>43,39; 316,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 117,56</t>
+          <t>-12,3; 115,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 97,76</t>
+          <t>-18,6; 93,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,24; 176,68</t>
+          <t>48,97; 218,6</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-1,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,26</t>
+          <t>-3,61; 0,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; -0,11</t>
+          <t>-4,13; -0,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -1,8</t>
+          <t>-4,93; -1,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,21</t>
+          <t>-0,78; 3,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,52</t>
+          <t>-1,98; 1,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,91</t>
+          <t>-1,27; 2,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,16</t>
+          <t>-1,45; 1,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,24</t>
+          <t>-2,45; 0,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,48</t>
+          <t>-2,58; -0,09</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-70,68%</t>
+          <t>-62,04%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-42,17%</t>
+          <t>-31,84%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 7,67</t>
+          <t>-59,46; 8,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,58; -0,1</t>
+          <t>-67,25; 1,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-89,25; -46,67</t>
+          <t>-79,26; -30,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 134,86</t>
+          <t>-23,29; 127,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 62,19</t>
+          <t>-48,86; 76,86</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 88,67</t>
+          <t>-31,58; 86,84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 35,79</t>
+          <t>-31,59; 42,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 6,92</t>
+          <t>-52,49; 6,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-66,09; -13,06</t>
+          <t>-51,9; -0,17</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,79</t>
+          <t>-1,18; 0,78</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,8</t>
+          <t>-2,43; -0,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,33</t>
+          <t>-0,61; 1,5</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,3</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,76</t>
+          <t>-0,91; 0,85</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,18</t>
+          <t>1,76; 3,54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,24</t>
+          <t>-0,07; 1,32</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,21</t>
+          <t>-1,42; -0,22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,95</t>
+          <t>0,96; 2,25</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,32</t>
+          <t>-26,62; 22,06</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -21,45</t>
+          <t>-53,62; -20,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 36,84</t>
+          <t>-13,09; 41,45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11,17; 84,88</t>
+          <t>13,0; 85,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 27,5</t>
+          <t>-25,83; 32,47</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>32,24; 116,92</t>
+          <t>46,96; 129,73</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 37,37</t>
+          <t>-1,86; 38,92</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-38,48; -7,08</t>
+          <t>-36,96; -6,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,12; 58,92</t>
+          <t>23,91; 68,6</t>
         </is>
       </c>
     </row>
